--- a/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 16,47</t>
+          <t>-21,15; 16,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 18,09</t>
+          <t>-10,26; 18,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,59; 9,81</t>
+          <t>-27,8; 9,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 41,13</t>
+          <t>-7,14; 38,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,4; 106,38</t>
+          <t>-55,6; 87,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 216,04</t>
+          <t>-49,07; 216,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,76; 69,52</t>
+          <t>-76,55; 85,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 173,56</t>
+          <t>-15,94; 146,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 15,48</t>
+          <t>-15,22; 15,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 16,71</t>
+          <t>-5,45; 15,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 16,81</t>
+          <t>-4,72; 15,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,46; 2,28</t>
+          <t>-30,75; 2,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 44,43</t>
+          <t>-33,71; 47,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 201,94</t>
+          <t>-36,27; 197,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-43,53; 357,29</t>
+          <t>-40,08; 379,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; 6,19</t>
+          <t>-62,37; 6,55</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 21,21</t>
+          <t>-26,46; 19,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 14,45</t>
+          <t>-12,22; 14,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 12,36</t>
+          <t>-12,93; 13,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,6; 40,73</t>
+          <t>5,77; 40,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-49,95; 70,9</t>
+          <t>-50,17; 65,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,83; 538,8</t>
+          <t>-83,87; 708,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,09; 264,09</t>
+          <t>-74,8; 279,58</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,42; 251,35</t>
+          <t>13,05; 236,71</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,91; 20,64</t>
+          <t>-18,77; 20,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,72; 25,91</t>
+          <t>-9,86; 26,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 5,83</t>
+          <t>-23,69; 5,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,19; -2,18</t>
+          <t>-38,58; -3,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 56,59</t>
+          <t>-35,7; 56,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,77; 321,34</t>
+          <t>-45,01; 283,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 227,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,96; -12,24</t>
+          <t>-87,01; -13,59</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 8,17</t>
+          <t>-10,81; 8,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 11,17</t>
+          <t>-2,75; 11,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 5,62</t>
+          <t>-8,71; 5,35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,32; 5,33</t>
+          <t>-18,82; 4,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 22,62</t>
+          <t>-24,67; 23,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-18,23; 102,95</t>
+          <t>-17,52; 110,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 57,72</t>
+          <t>-50,38; 45,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 17,77</t>
+          <t>-48,87; 14,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,0</t>
+          <t>17,67</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 16,18</t>
+          <t>-22,39; 16,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,26; 18,34</t>
+          <t>-11,42; 17,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 9,57</t>
+          <t>-27,05; 8,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 38,99</t>
+          <t>-6,84; 40,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-55,6; 87,14</t>
+          <t>-58,47; 92,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,07; 216,89</t>
+          <t>-49,53; 195,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 85,94</t>
+          <t>-77,33; 60,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-15,94; 146,16</t>
+          <t>-18,31; 152,43</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-14,16</t>
+          <t>-14,39</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-33,64%</t>
+          <t>-32,75%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 15,81</t>
+          <t>-16,14; 15,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 15,52</t>
+          <t>-6,49; 15,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 15,99</t>
+          <t>-5,77; 16,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 2,27</t>
+          <t>-32,15; 0,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-33,71; 47,49</t>
+          <t>-34,33; 47,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 197,09</t>
+          <t>-39,32; 208,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-40,08; 379,78</t>
+          <t>-46,7; 376,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 6,55</t>
+          <t>-60,29; 4,58</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,31</t>
+          <t>22,27</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 19,37</t>
+          <t>-25,03; 20,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 14,97</t>
+          <t>-12,01; 14,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,93; 13,24</t>
+          <t>-13,05; 13,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,77; 40,5</t>
+          <t>3,9; 40,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 65,11</t>
+          <t>-48,86; 68,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,87; 708,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,8; 279,58</t>
+          <t>-76,3; 360,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,05; 236,71</t>
+          <t>9,32; 222,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-18,06</t>
+          <t>-9,06</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-55,8%</t>
+          <t>-28,12%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,77; 20,25</t>
+          <t>-17,79; 20,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 26,76</t>
+          <t>-12,37; 27,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,69; 5,76</t>
+          <t>-24,15; 5,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-38,58; -3,83</t>
+          <t>-24,86; 5,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,7; 56,59</t>
+          <t>-33,63; 61,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 283,59</t>
+          <t>-49,42; 286,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 227,23</t>
+          <t>-100,0; 200,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,01; -13,59</t>
+          <t>-61,57; 25,62</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,08</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-15,13%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 8,21</t>
+          <t>-11,39; 8,41</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 11,66</t>
+          <t>-3,18; 10,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 5,35</t>
+          <t>-8,63; 5,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 4,52</t>
+          <t>-9,03; 9,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-24,67; 23,79</t>
+          <t>-26,31; 23,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,52; 110,75</t>
+          <t>-18,56; 101,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 45,66</t>
+          <t>-50,61; 55,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-48,87; 14,21</t>
+          <t>-23,51; 31,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16_n_R2-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-2,3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-8,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17,67</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-7,98%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>17,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-34,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>49,91%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>0.2107055573799185</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.4989314168042137</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.46174231137472</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>2.223623191458925</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.02996874243189196</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1138572839797891</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.3054925315850822</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.1820961143821843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-22,39; 16,66</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,42; 17,58</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-27,05; 8,21</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,84; 40,18</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-58,47; 92,56</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-49,53; 195,13</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-77,33; 60,98</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-18,31; 152,43</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.071380496428593</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.662604753589283</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.462064458995696</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-6.300381084500274</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5589099346914211</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.5814631752680236</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.7691831318279968</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4248354237537728</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>5.688152577696535</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.405628397997384</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>2.466661903613675</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>11.75667238384853</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.297024617137114</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.973588202217571</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.0262815185014</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.532174649260253</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>4,39</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,36</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-14,39</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,3%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>34,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>58,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-32,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-16,14; 15,18</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-6,49; 15,88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-5,77; 16,61</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-32,15; 0,87</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-34,33; 47,16</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-39,32; 208,43</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-46,7; 376,88</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-60,29; 4,58</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-1.260897471772152</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.7373998378521054</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.385066689421993</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-3.243299151713801</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1525901909680737</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.230719840716939</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.9007349202113979</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.2808002858282955</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,1</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-7,38%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>25,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,21%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>84,61%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.038478824877017</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-1.860104371095508</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-0.7310430375096327</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-9.361203428090656</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.4897417700284438</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4302980047023083</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.4778695148200241</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.6212602446766583</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-25,03; 20,23</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-12,01; 14,35</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-13,05; 13,72</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 40,78</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-48,86; 68,18</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-76,3; 360,59</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>9,32; 222,75</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.603280632176064</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.707887204312219</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>3.684272161162351</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>2.17223341928955</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.4086388062244117</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.885747111739149</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>5.462577034593568</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.269936241284875</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,09</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-8,86</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-9,06</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-60,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-28,12%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.2185989320963311</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5329291939102289</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.2235963149603407</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.82634495540943</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.03089337184211785</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.3449562685672937</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1128325709774455</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.8344657146920497</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,79; 20,99</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-12,37; 27,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-24,15; 5,31</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-24,86; 5,83</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-33,63; 61,15</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-49,42; 286,88</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 200,03</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-61,57; 25,62</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-4.984690587683663</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.275537262649207</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.306978226839137</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-0.2728071343317642</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.5368051905486896</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.8795569215957926</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7546476954022565</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.1056165840777736</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.791547822362417</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.019655706080619</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.673845753185604</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.90654500032025</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.06315161997465</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>6.615467546716598</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.383312732158066</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.527130363608628</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.517868558210199</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.47856772913549</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.178252496541585</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-2.349729581635482</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1762290336262124</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.6006562871328562</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.6118037786185041</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.3423516913827907</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.880010774116068</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.461217318141446</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.307911284263779</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.958158287119771</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5450194639169614</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.4670374934649909</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.6751995296900054</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.504863870690022</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>4.733365374691116</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.5446619569514438</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.8318427951910463</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.4034742311040536</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>3.524903310311801</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.556675132222452</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.1797298272908103</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,24</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-3,85%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-9,02%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-11,39; 8,41</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 10,68</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-8,63; 5,45</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-9,03; 9,45</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-26,31; 23,04</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-18,56; 101,71</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-50,61; 55,0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-23,51; 31,83</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-0.8845601850296481</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.8161231071238287</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-0.01208570152467746</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.08806494941568654</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.1116373913155507</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.280956543191493</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.005295870280581951</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.01102041115561363</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-3.082796076147634</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-0.6879490424069717</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.22317471121803</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.565536708011636</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.3495106760527131</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.2045587313896238</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.4327395411556695</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.2820297128167414</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.441513528997812</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.544337762016866</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.18784936892884</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2.319354524663664</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.212741403429535</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.205557806914321</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.7238265048067668</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3328319999024059</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
